--- a/____EvoM1_TraitTable/manipulation.xlsx
+++ b/____EvoM1_TraitTable/manipulation.xlsx
@@ -1439,13 +1439,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{589AC951-0F03-440E-AA7D-5BA4BAF704D1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{823C3306-C08E-4390-8B18-233D5F9692E3}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{18C7E1C5-103B-4708-8243-6F3E467095EF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{39DF8387-75E9-40CF-9CF8-18DE4CF2D008}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0C3714B7-E5AF-48D2-BA09-054C05EAFB17}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4FCFFDF8-EC70-4FFA-925D-DD7CC099F825}"/>
 </file>
--- a/____EvoM1_TraitTable/manipulation.xlsx
+++ b/____EvoM1_TraitTable/manipulation.xlsx
@@ -1439,13 +1439,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{823C3306-C08E-4390-8B18-233D5F9692E3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3A8E5FE5-1F1C-4120-9D60-7198C01D3A68}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{39DF8387-75E9-40CF-9CF8-18DE4CF2D008}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{41834E08-FE79-4CAE-8A8D-635D38D62D3A}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4FCFFDF8-EC70-4FFA-925D-DD7CC099F825}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2915C5EF-6A6A-4BED-B3D8-DEB05A0C68FC}"/>
 </file>
--- a/____EvoM1_TraitTable/manipulation.xlsx
+++ b/____EvoM1_TraitTable/manipulation.xlsx
@@ -1439,13 +1439,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3A8E5FE5-1F1C-4120-9D60-7198C01D3A68}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74A9B5DC-3445-4534-BBDC-21C4209926A9}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{41834E08-FE79-4CAE-8A8D-635D38D62D3A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D1733A66-FB4E-48C1-A5C9-77F7B43B6B9A}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2915C5EF-6A6A-4BED-B3D8-DEB05A0C68FC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{15AF48F2-3614-4609-9ACF-EDA0AF806556}"/>
 </file>
--- a/____EvoM1_TraitTable/manipulation.xlsx
+++ b/____EvoM1_TraitTable/manipulation.xlsx
@@ -1439,13 +1439,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74A9B5DC-3445-4534-BBDC-21C4209926A9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C450AE25-33D5-4987-85C2-3419BB2AD019}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D1733A66-FB4E-48C1-A5C9-77F7B43B6B9A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1E9473F0-F9FF-444F-84E2-C9EFF1C55FB7}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{15AF48F2-3614-4609-9ACF-EDA0AF806556}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D71A8D39-9334-4932-A688-BC28EFE5DA24}"/>
 </file>
--- a/____EvoM1_TraitTable/manipulation.xlsx
+++ b/____EvoM1_TraitTable/manipulation.xlsx
@@ -11,6 +11,140 @@
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="43">
+  <si>
+    <t>species_sci</t>
+  </si>
+  <si>
+    <t>Species</t>
+  </si>
+  <si>
+    <t>Manipulation_complexity</t>
+  </si>
+  <si>
+    <t>Tool_use</t>
+  </si>
+  <si>
+    <t>Extractive_foraging</t>
+  </si>
+  <si>
+    <t>Ateles fusciceps</t>
+  </si>
+  <si>
+    <t>Ateles geoffroyi</t>
+  </si>
+  <si>
+    <t>Callicebus cupreus</t>
+  </si>
+  <si>
+    <t>Callimico goeldii</t>
+  </si>
+  <si>
+    <t>Callithrix geoffroyi</t>
+  </si>
+  <si>
+    <t>Callithrix jacchus</t>
+  </si>
+  <si>
+    <t>Cercocebus atys</t>
+  </si>
+  <si>
+    <t>Cercopithecus diana</t>
+  </si>
+  <si>
+    <t>Cercopithecus hamlyni</t>
+  </si>
+  <si>
+    <t>Cercopithecus lhoesti</t>
+  </si>
+  <si>
+    <t>Colobus guereza</t>
+  </si>
+  <si>
+    <t>Eulemur coronatus</t>
+  </si>
+  <si>
+    <t>Eulemur macaco</t>
+  </si>
+  <si>
+    <t>Gorilla gorilla</t>
+  </si>
+  <si>
+    <t>Hapalemur griseus</t>
+  </si>
+  <si>
+    <t>Homo sapiens</t>
+  </si>
+  <si>
+    <t>Hylobates pileatus</t>
+  </si>
+  <si>
+    <t>Lemur catta</t>
+  </si>
+  <si>
+    <t>Leontopithecus chrysomelas</t>
+  </si>
+  <si>
+    <t>Leontopithecus rosalia</t>
+  </si>
+  <si>
+    <t>Macaca fascicularis</t>
+  </si>
+  <si>
+    <t>Macaca sylvanus</t>
+  </si>
+  <si>
+    <t>Macaca tonkeana</t>
+  </si>
+  <si>
+    <t>Mandrillus sphinx</t>
+  </si>
+  <si>
+    <t>Pan troglodytes</t>
+  </si>
+  <si>
+    <t>Pithecia pithecia</t>
+  </si>
+  <si>
+    <t>Pongo sp.</t>
+  </si>
+  <si>
+    <t>Pongo abelii</t>
+  </si>
+  <si>
+    <t>Propithecus verreauxi</t>
+  </si>
+  <si>
+    <t>Saguinus bicolor</t>
+  </si>
+  <si>
+    <t>Saguinus imperator</t>
+  </si>
+  <si>
+    <t>Saguinus labiatus</t>
+  </si>
+  <si>
+    <t>Saguinus oedipus</t>
+  </si>
+  <si>
+    <t>Saimiri sciureus</t>
+  </si>
+  <si>
+    <t>Sapajus apella</t>
+  </si>
+  <si>
+    <t>Symphalangus syndactylus</t>
+  </si>
+  <si>
+    <t>Theropithecus gelada</t>
+  </si>
+  <si>
+    <t>Varecia rubra</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -354,43 +488,29 @@
   <dimension ref="A1:E38"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>species_sci</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Species</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Manipulation_complexity</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Tool_use</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Extractive_foraging</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Ateles fusciceps</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Ateles fusciceps</t>
-        </is>
+    <row r="1" spans="1:5" s="1" customFormat="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
       </c>
       <c r="C2">
         <v>1.35</v>
@@ -402,16 +522,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Ateles geoffroyi</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Ateles geoffroyi</t>
-        </is>
+    <row r="3" spans="1:5">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
       </c>
       <c r="C3">
         <v>2.48</v>
@@ -423,16 +539,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Callicebus cupreus</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Callicebus cupreus</t>
-        </is>
+    <row r="4" spans="1:5">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
       </c>
       <c r="C4">
         <v>1.85</v>
@@ -444,16 +556,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Callimico goeldii</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Callimico goeldii</t>
-        </is>
+    <row r="5" spans="1:5">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>8</v>
       </c>
       <c r="C5">
         <v>1.43</v>
@@ -465,16 +573,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Callithrix geoffroyi</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Callithrix geoffroyi</t>
-        </is>
+    <row r="6" spans="1:5">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" t="s">
+        <v>9</v>
       </c>
       <c r="C6">
         <v>1.32</v>
@@ -486,16 +590,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Callithrix jacchus</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Callithrix jacchus</t>
-        </is>
+    <row r="7" spans="1:5">
+      <c r="A7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" t="s">
+        <v>10</v>
       </c>
       <c r="C7">
         <v>1.33</v>
@@ -507,16 +607,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Cercocebus atys</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Cercocebus atys</t>
-        </is>
+    <row r="8" spans="1:5">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" t="s">
+        <v>11</v>
       </c>
       <c r="C8">
         <v>2.24</v>
@@ -528,16 +624,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Cercopithecus diana</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Cercopithecus diana</t>
-        </is>
+    <row r="9" spans="1:5">
+      <c r="A9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" t="s">
+        <v>12</v>
       </c>
       <c r="C9">
         <v>2.03</v>
@@ -549,16 +641,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Cercopithecus hamlyni</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Cercopithecus hamlyni</t>
-        </is>
+    <row r="10" spans="1:5">
+      <c r="A10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" t="s">
+        <v>13</v>
       </c>
       <c r="C10">
         <v>3.84</v>
@@ -570,16 +658,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Cercopithecus lhoesti</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Cercopithecus lhoesti</t>
-        </is>
+    <row r="11" spans="1:5">
+      <c r="A11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" t="s">
+        <v>14</v>
       </c>
       <c r="C11">
         <v>2.77</v>
@@ -591,16 +675,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Colobus guereza</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Colobus guereza</t>
-        </is>
+    <row r="12" spans="1:5">
+      <c r="A12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" t="s">
+        <v>15</v>
       </c>
       <c r="C12">
         <v>2.38</v>
@@ -612,16 +692,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Eulemur coronatus</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Eulemur coronatus</t>
-        </is>
+    <row r="13" spans="1:5">
+      <c r="A13" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" t="s">
+        <v>16</v>
       </c>
       <c r="C13">
         <v>1.6</v>
@@ -633,16 +709,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Eulemur macaco</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Eulemur macaco</t>
-        </is>
+    <row r="14" spans="1:5">
+      <c r="A14" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" t="s">
+        <v>17</v>
       </c>
       <c r="C14">
         <v>1.23</v>
@@ -654,16 +726,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Gorilla gorilla</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Gorilla gorilla</t>
-        </is>
+    <row r="15" spans="1:5">
+      <c r="A15" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15" t="s">
+        <v>18</v>
       </c>
       <c r="C15">
         <v>5</v>
@@ -675,16 +743,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Hapalemur griseus</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Hapalemur griseus</t>
-        </is>
+    <row r="16" spans="1:5">
+      <c r="A16" t="s">
+        <v>19</v>
+      </c>
+      <c r="B16" t="s">
+        <v>19</v>
       </c>
       <c r="C16">
         <v>1.78</v>
@@ -696,16 +760,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Homo sapiens</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Homo sapiens</t>
-        </is>
+    <row r="17" spans="1:5">
+      <c r="A17" t="s">
+        <v>20</v>
+      </c>
+      <c r="B17" t="s">
+        <v>20</v>
       </c>
       <c r="C17">
         <v>5.4</v>
@@ -717,16 +777,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Hylobates pileatus</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Hylobates pileatus</t>
-        </is>
+    <row r="18" spans="1:5">
+      <c r="A18" t="s">
+        <v>21</v>
+      </c>
+      <c r="B18" t="s">
+        <v>21</v>
       </c>
       <c r="C18">
         <v>2.14</v>
@@ -738,16 +794,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Lemur catta</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Lemur catta</t>
-        </is>
+    <row r="19" spans="1:5">
+      <c r="A19" t="s">
+        <v>22</v>
+      </c>
+      <c r="B19" t="s">
+        <v>22</v>
       </c>
       <c r="C19">
         <v>1.48</v>
@@ -759,16 +811,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Leontopithecus chrysomelas</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Leontopithecus chrysomelas</t>
-        </is>
+    <row r="20" spans="1:5">
+      <c r="A20" t="s">
+        <v>23</v>
+      </c>
+      <c r="B20" t="s">
+        <v>23</v>
       </c>
       <c r="C20">
         <v>1.63</v>
@@ -780,16 +828,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Leontopithecus rosalia</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Leontopithecus rosalia</t>
-        </is>
+    <row r="21" spans="1:5">
+      <c r="A21" t="s">
+        <v>24</v>
+      </c>
+      <c r="B21" t="s">
+        <v>24</v>
       </c>
       <c r="C21">
         <v>1.2</v>
@@ -801,16 +845,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Macaca fascicularis</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Macaca fascicularis</t>
-        </is>
+    <row r="22" spans="1:5">
+      <c r="A22" t="s">
+        <v>25</v>
+      </c>
+      <c r="B22" t="s">
+        <v>25</v>
       </c>
       <c r="C22">
         <v>4.11</v>
@@ -822,16 +862,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Macaca sylvanus</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Macaca sylvanus</t>
-        </is>
+    <row r="23" spans="1:5">
+      <c r="A23" t="s">
+        <v>26</v>
+      </c>
+      <c r="B23" t="s">
+        <v>26</v>
       </c>
       <c r="C23">
         <v>3.76</v>
@@ -843,16 +879,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Macaca tonkeana</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Macaca tonkeana</t>
-        </is>
+    <row r="24" spans="1:5">
+      <c r="A24" t="s">
+        <v>27</v>
+      </c>
+      <c r="B24" t="s">
+        <v>27</v>
       </c>
       <c r="C24">
         <v>3</v>
@@ -864,16 +896,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Mandrillus sphinx</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Mandrillus sphinx</t>
-        </is>
+    <row r="25" spans="1:5">
+      <c r="A25" t="s">
+        <v>28</v>
+      </c>
+      <c r="B25" t="s">
+        <v>28</v>
       </c>
       <c r="C25">
         <v>2.21</v>
@@ -885,16 +913,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Pan troglodytes</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Pan troglodytes</t>
-        </is>
+    <row r="26" spans="1:5">
+      <c r="A26" t="s">
+        <v>29</v>
+      </c>
+      <c r="B26" t="s">
+        <v>29</v>
       </c>
       <c r="C26">
         <v>4.38</v>
@@ -906,16 +930,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Pithecia pithecia</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Pithecia pithecia</t>
-        </is>
+    <row r="27" spans="1:5">
+      <c r="A27" t="s">
+        <v>30</v>
+      </c>
+      <c r="B27" t="s">
+        <v>30</v>
       </c>
       <c r="C27">
         <v>1.86</v>
@@ -927,16 +947,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Pongo sp.</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Pongo abelii</t>
-        </is>
+    <row r="28" spans="1:5">
+      <c r="A28" t="s">
+        <v>31</v>
+      </c>
+      <c r="B28" t="s">
+        <v>32</v>
       </c>
       <c r="C28">
         <v>3.89</v>
@@ -948,16 +964,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Propithecus verreauxi</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Propithecus verreauxi</t>
-        </is>
+    <row r="29" spans="1:5">
+      <c r="A29" t="s">
+        <v>33</v>
+      </c>
+      <c r="B29" t="s">
+        <v>33</v>
       </c>
       <c r="C29">
         <v>1.44</v>
@@ -969,16 +981,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Saguinus bicolor</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Saguinus bicolor</t>
-        </is>
+    <row r="30" spans="1:5">
+      <c r="A30" t="s">
+        <v>34</v>
+      </c>
+      <c r="B30" t="s">
+        <v>34</v>
       </c>
       <c r="C30">
         <v>1</v>
@@ -990,16 +998,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Saguinus imperator</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Saguinus imperator</t>
-        </is>
+    <row r="31" spans="1:5">
+      <c r="A31" t="s">
+        <v>35</v>
+      </c>
+      <c r="B31" t="s">
+        <v>35</v>
       </c>
       <c r="C31">
         <v>1.62</v>
@@ -1011,16 +1015,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Saguinus labiatus</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Saguinus labiatus</t>
-        </is>
+    <row r="32" spans="1:5">
+      <c r="A32" t="s">
+        <v>36</v>
+      </c>
+      <c r="B32" t="s">
+        <v>36</v>
       </c>
       <c r="C32">
         <v>2.27</v>
@@ -1032,16 +1032,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Saguinus oedipus</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Saguinus oedipus</t>
-        </is>
+    <row r="33" spans="1:5">
+      <c r="A33" t="s">
+        <v>37</v>
+      </c>
+      <c r="B33" t="s">
+        <v>37</v>
       </c>
       <c r="C33">
         <v>1.7</v>
@@ -1053,16 +1049,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Saimiri sciureus</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Saimiri sciureus</t>
-        </is>
+    <row r="34" spans="1:5">
+      <c r="A34" t="s">
+        <v>38</v>
+      </c>
+      <c r="B34" t="s">
+        <v>38</v>
       </c>
       <c r="C34">
         <v>1.94</v>
@@ -1074,16 +1066,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Sapajus apella</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Sapajus apella</t>
-        </is>
+    <row r="35" spans="1:5">
+      <c r="A35" t="s">
+        <v>39</v>
+      </c>
+      <c r="B35" t="s">
+        <v>39</v>
       </c>
       <c r="C35">
         <v>2.54</v>
@@ -1095,16 +1083,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Symphalangus syndactylus</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Symphalangus syndactylus</t>
-        </is>
+    <row r="36" spans="1:5">
+      <c r="A36" t="s">
+        <v>40</v>
+      </c>
+      <c r="B36" t="s">
+        <v>40</v>
       </c>
       <c r="C36">
         <v>3.08</v>
@@ -1116,16 +1100,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Theropithecus gelada</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Theropithecus gelada</t>
-        </is>
+    <row r="37" spans="1:5">
+      <c r="A37" t="s">
+        <v>41</v>
+      </c>
+      <c r="B37" t="s">
+        <v>41</v>
       </c>
       <c r="C37">
         <v>4.17</v>
@@ -1137,16 +1117,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Varecia rubra</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Varecia rubra</t>
-        </is>
+    <row r="38" spans="1:5">
+      <c r="A38" t="s">
+        <v>42</v>
+      </c>
+      <c r="B38" t="s">
+        <v>42</v>
       </c>
       <c r="C38">
         <v>1.33</v>
@@ -1439,13 +1415,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C450AE25-33D5-4987-85C2-3419BB2AD019}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6795C3A2-344C-4E4E-8EBC-EB02B02B4980}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1E9473F0-F9FF-444F-84E2-C9EFF1C55FB7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B3B93B8-0471-4579-825E-7F7F2BB5E381}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D71A8D39-9334-4932-A688-BC28EFE5DA24}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A07DF637-D49D-41A5-9DE1-7C20AA905C1B}"/>
 </file>
--- a/____EvoM1_TraitTable/manipulation.xlsx
+++ b/____EvoM1_TraitTable/manipulation.xlsx
@@ -1415,13 +1415,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6795C3A2-344C-4E4E-8EBC-EB02B02B4980}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0EF08D66-58B3-4710-AE48-68A5114F5CA7}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B3B93B8-0471-4579-825E-7F7F2BB5E381}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4EAC159D-F22B-4ECB-8115-8CF43F7AF899}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A07DF637-D49D-41A5-9DE1-7C20AA905C1B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{43FAE068-C98B-4913-8DAA-B58592B37E86}"/>
 </file>
--- a/____EvoM1_TraitTable/manipulation.xlsx
+++ b/____EvoM1_TraitTable/manipulation.xlsx
@@ -1415,13 +1415,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0EF08D66-58B3-4710-AE48-68A5114F5CA7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{26BCA596-2DCE-423B-A9CE-4B9B81D3CD8D}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4EAC159D-F22B-4ECB-8115-8CF43F7AF899}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1E567FA2-4772-4A63-88F4-907646DB65B5}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{43FAE068-C98B-4913-8DAA-B58592B37E86}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DFABB1A9-59FF-4257-930B-1F350F9DB788}"/>
 </file>
--- a/____EvoM1_TraitTable/manipulation.xlsx
+++ b/____EvoM1_TraitTable/manipulation.xlsx
@@ -1137,291 +1137,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
-    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{26BCA596-2DCE-423B-A9CE-4B9B81D3CD8D}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1E567FA2-4772-4A63-88F4-907646DB65B5}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DFABB1A9-59FF-4257-930B-1F350F9DB788}"/>
 </file>
--- a/____EvoM1_TraitTable/manipulation.xlsx
+++ b/____EvoM1_TraitTable/manipulation.xlsx
@@ -1137,4 +1137,291 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
+    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E7894855-4701-4E3E-A03A-D1FE04E5D32B}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B4B22B34-C84C-458F-B7CF-4481EB6FC497}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{88A871B5-0717-4736-9CF9-74CF8BB958A6}"/>
 </file>
--- a/____EvoM1_TraitTable/manipulation.xlsx
+++ b/____EvoM1_TraitTable/manipulation.xlsx
@@ -1137,291 +1137,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
-    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E7894855-4701-4E3E-A03A-D1FE04E5D32B}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B4B22B34-C84C-458F-B7CF-4481EB6FC497}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{88A871B5-0717-4736-9CF9-74CF8BB958A6}"/>
 </file>
--- a/____EvoM1_TraitTable/manipulation.xlsx
+++ b/____EvoM1_TraitTable/manipulation.xlsx
@@ -1137,4 +1137,291 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
+    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3D644418-B58B-486B-8B36-D896E9CDAA50}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{368EC2E4-D1F6-4EAC-96AB-7610646CAED7}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{84E8A33A-4864-4FEA-B36F-E41E82C5B389}"/>
 </file>
--- a/____EvoM1_TraitTable/manipulation.xlsx
+++ b/____EvoM1_TraitTable/manipulation.xlsx
@@ -1415,13 +1415,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3D644418-B58B-486B-8B36-D896E9CDAA50}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A9B30BA7-621F-4484-B203-5339E7D505FA}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{368EC2E4-D1F6-4EAC-96AB-7610646CAED7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1ABAAAFA-F02E-440D-9ED0-71C50309547C}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{84E8A33A-4864-4FEA-B36F-E41E82C5B389}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59F5CCCB-9EB8-49C7-960C-8488B082EDB1}"/>
 </file>
--- a/____EvoM1_TraitTable/manipulation.xlsx
+++ b/____EvoM1_TraitTable/manipulation.xlsx
@@ -1415,13 +1415,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A9B30BA7-621F-4484-B203-5339E7D505FA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DC3ACC8B-C099-4392-84E0-5E5526C81AB9}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1ABAAAFA-F02E-440D-9ED0-71C50309547C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B24F09E7-F228-452D-8532-EE3833515AEF}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59F5CCCB-9EB8-49C7-960C-8488B082EDB1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5D85B5CB-7B94-4132-A7CC-9A9B216C3AFD}"/>
 </file>
--- a/____EvoM1_TraitTable/manipulation.xlsx
+++ b/____EvoM1_TraitTable/manipulation.xlsx
@@ -1415,13 +1415,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DC3ACC8B-C099-4392-84E0-5E5526C81AB9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{98F75B54-3F89-4039-A9FC-2712615277E7}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B24F09E7-F228-452D-8532-EE3833515AEF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{17A686E7-3AB7-4050-A2DF-76A603D0541A}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5D85B5CB-7B94-4132-A7CC-9A9B216C3AFD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C098C31E-F6C6-472D-AC0A-1552F261E73B}"/>
 </file>
--- a/____EvoM1_TraitTable/manipulation.xlsx
+++ b/____EvoM1_TraitTable/manipulation.xlsx
@@ -1415,13 +1415,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{98F75B54-3F89-4039-A9FC-2712615277E7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6035C8C8-B498-498E-93E5-AD111634B3F3}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{17A686E7-3AB7-4050-A2DF-76A603D0541A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC2E751C-50D8-42C4-97DD-D52383F02E74}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C098C31E-F6C6-472D-AC0A-1552F261E73B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B1654F21-F21F-4E2B-AF07-3AC259C399B8}"/>
 </file>
--- a/____EvoM1_TraitTable/manipulation.xlsx
+++ b/____EvoM1_TraitTable/manipulation.xlsx
@@ -1415,13 +1415,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6035C8C8-B498-498E-93E5-AD111634B3F3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D607D3E4-D0EA-4010-B662-857C79B57F81}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC2E751C-50D8-42C4-97DD-D52383F02E74}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C6AA2B90-E786-4331-8772-2C762E51C796}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B1654F21-F21F-4E2B-AF07-3AC259C399B8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E4A960B-B990-4020-BB4E-85CE8EACE1F0}"/>
 </file>
--- a/____EvoM1_TraitTable/manipulation.xlsx
+++ b/____EvoM1_TraitTable/manipulation.xlsx
@@ -1137,291 +1137,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
-    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D607D3E4-D0EA-4010-B662-857C79B57F81}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C6AA2B90-E786-4331-8772-2C762E51C796}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E4A960B-B990-4020-BB4E-85CE8EACE1F0}"/>
 </file>
--- a/____EvoM1_TraitTable/manipulation.xlsx
+++ b/____EvoM1_TraitTable/manipulation.xlsx
@@ -1137,4 +1137,291 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
+    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{838764F1-EAA7-4B49-9317-1D4D852FBE95}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{10E7674F-884A-4118-898C-A873C6CCDF4F}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA55059E-3C5C-4F78-88FE-56B0FE215638}"/>
 </file>
--- a/____EvoM1_TraitTable/manipulation.xlsx
+++ b/____EvoM1_TraitTable/manipulation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="42">
   <si>
     <t>species_sci</t>
   </si>
@@ -107,9 +107,6 @@
   </si>
   <si>
     <t>Pithecia pithecia</t>
-  </si>
-  <si>
-    <t>Pongo sp.</t>
   </si>
   <si>
     <t>Pongo abelii</t>
@@ -952,7 +949,7 @@
         <v>31</v>
       </c>
       <c r="B28" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C28">
         <v>3.89</v>
@@ -966,10 +963,10 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B29" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C29">
         <v>1.44</v>
@@ -983,10 +980,10 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B30" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C30">
         <v>1</v>
@@ -1000,10 +997,10 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B31" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C31">
         <v>1.62</v>
@@ -1017,10 +1014,10 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B32" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C32">
         <v>2.27</v>
@@ -1034,10 +1031,10 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B33" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C33">
         <v>1.7</v>
@@ -1051,10 +1048,10 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B34" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C34">
         <v>1.94</v>
@@ -1068,10 +1065,10 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B35" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C35">
         <v>2.54</v>
@@ -1085,10 +1082,10 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B36" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C36">
         <v>3.08</v>
@@ -1102,10 +1099,10 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B37" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C37">
         <v>4.17</v>
@@ -1119,10 +1116,10 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B38" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C38">
         <v>1.33</v>
@@ -1415,13 +1412,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{838764F1-EAA7-4B49-9317-1D4D852FBE95}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{98702F04-12A3-44A1-835C-FACE2EAD7197}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{10E7674F-884A-4118-898C-A873C6CCDF4F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8F672B10-BB42-461E-9BF6-ABB0ACB08005}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA55059E-3C5C-4F78-88FE-56B0FE215638}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A8A467F9-9645-46A3-A3A8-7D5995AA47EF}"/>
 </file>
--- a/____EvoM1_TraitTable/manipulation.xlsx
+++ b/____EvoM1_TraitTable/manipulation.xlsx
@@ -1412,13 +1412,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{98702F04-12A3-44A1-835C-FACE2EAD7197}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FF8B62DA-E534-4456-8747-5F31FA0B7845}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8F672B10-BB42-461E-9BF6-ABB0ACB08005}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5CD9DFCB-CBEA-44D4-9CF1-FB8168D82082}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A8A467F9-9645-46A3-A3A8-7D5995AA47EF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5F2523DC-49B9-4457-A5FB-527113DB42FE}"/>
 </file>
--- a/____EvoM1_TraitTable/manipulation.xlsx
+++ b/____EvoM1_TraitTable/manipulation.xlsx
@@ -1412,13 +1412,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FF8B62DA-E534-4456-8747-5F31FA0B7845}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C5C79C9-ED94-41E4-8B86-056BB779DCEF}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5CD9DFCB-CBEA-44D4-9CF1-FB8168D82082}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A08A8A6F-DB5E-46DA-9C04-368C7C838CF2}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5F2523DC-49B9-4457-A5FB-527113DB42FE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E94D8992-A3AD-42AB-9B16-8BA77F2F3F9D}"/>
 </file>
--- a/____EvoM1_TraitTable/manipulation.xlsx
+++ b/____EvoM1_TraitTable/manipulation.xlsx
@@ -1412,13 +1412,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C5C79C9-ED94-41E4-8B86-056BB779DCEF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2F40CD1F-8255-4830-A5FA-FAF9C714081D}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A08A8A6F-DB5E-46DA-9C04-368C7C838CF2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{613964FD-F586-4D35-B7D9-A775218B931F}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E94D8992-A3AD-42AB-9B16-8BA77F2F3F9D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CCAEC6A4-8735-4708-B379-42509DA07C8F}"/>
 </file>
--- a/____EvoM1_TraitTable/manipulation.xlsx
+++ b/____EvoM1_TraitTable/manipulation.xlsx
@@ -1412,13 +1412,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2F40CD1F-8255-4830-A5FA-FAF9C714081D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0F489B97-670B-49A1-A81E-222C0DF438CA}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{613964FD-F586-4D35-B7D9-A775218B931F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{72F57C22-AA85-4AEE-91C5-0DEBB0B391F3}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CCAEC6A4-8735-4708-B379-42509DA07C8F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{232F95A5-C7FC-462B-B456-1D502CBAC82A}"/>
 </file>
--- a/____EvoM1_TraitTable/manipulation.xlsx
+++ b/____EvoM1_TraitTable/manipulation.xlsx
@@ -1134,291 +1134,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
-    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0F489B97-670B-49A1-A81E-222C0DF438CA}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{72F57C22-AA85-4AEE-91C5-0DEBB0B391F3}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{232F95A5-C7FC-462B-B456-1D502CBAC82A}"/>
 </file>
--- a/____EvoM1_TraitTable/manipulation.xlsx
+++ b/____EvoM1_TraitTable/manipulation.xlsx
@@ -1134,4 +1134,291 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
+    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{21B59E0F-709E-4C4D-B360-2CBAF875235F}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EB8697C9-CF91-4FD8-83FE-E02EB6FD6457}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C1545879-A870-4CBF-BD38-1BA58E9B9FDA}"/>
 </file>